--- a/artfynd/A 50760-2023 artfynd.xlsx
+++ b/artfynd/A 50760-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>131834427</v>
       </c>
       <c r="B2" t="n">
-        <v>57807</v>
+        <v>57855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50760-2023 artfynd.xlsx
+++ b/artfynd/A 50760-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>131834427</v>
       </c>
       <c r="B2" t="n">
-        <v>57855</v>
+        <v>57865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50760-2023 artfynd.xlsx
+++ b/artfynd/A 50760-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>131834427</v>
       </c>
       <c r="B2" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50760-2023 artfynd.xlsx
+++ b/artfynd/A 50760-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>131834427</v>
       </c>
       <c r="B2" t="n">
-        <v>57866</v>
+        <v>57869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
